--- a/cotizaciones/Estimate_Yellowstone_Club_Stone_Floor.xlsx
+++ b/cotizaciones/Estimate_Yellowstone_Club_Stone_Floor.xlsx
@@ -560,7 +560,11 @@
           <t>Client:</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Tyler</t>
+        </is>
+      </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
     </row>
@@ -572,7 +576,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Yellowstone Club, Big Sky, MT</t>
+          <t>7 South Cabin Road, Yellowstone Club, Big Sky, MT</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>

--- a/cotizaciones/Estimate_Yellowstone_Club_Stone_Floor.xlsx
+++ b/cotizaciones/Estimate_Yellowstone_Club_Stone_Floor.xlsx
@@ -576,7 +576,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>7 South Cabin Road, Yellowstone Club, Big Sky, MT</t>
+          <t>7 South Cabin Road, American Spirit, Yellowstone Club, Big Sky, MT</t>
         </is>
       </c>
       <c r="D5" s="4" t="n"/>

--- a/cotizaciones/Estimate_Yellowstone_Club_Stone_Floor.xlsx
+++ b/cotizaciones/Estimate_Yellowstone_Club_Stone_Floor.xlsx
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>7915</v>
+        <v>10290</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>6375</v>
+        <v>8285</v>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>6820</v>
+        <v>8860</v>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>6180</v>
+        <v>8030</v>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>

--- a/cotizaciones/Estimate_Yellowstone_Club_Stone_Floor.xlsx
+++ b/cotizaciones/Estimate_Yellowstone_Club_Stone_Floor.xlsx
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>10290</v>
+        <v>11430</v>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>8285</v>
+        <v>9205</v>
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="D23" s="16" t="n">
-        <v>8860</v>
+        <v>9845</v>
       </c>
       <c r="E23" s="17" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>8030</v>
+        <v>8920</v>
       </c>
       <c r="E24" s="17" t="inlineStr">
         <is>
